--- a/etf_holdings/2026-10-30_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.50%4,200,000</t>
+          <t>14.79%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.50%</t>
+          <t>14.79%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5010</v>
+        <v>4675</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.67%1,350,000</t>
+          <t>9.38%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.67%</t>
+          <t>9.38%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%477</t>
+          <t>-4.72%454.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>477</v>
+        <v>454.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.98%11,700,000</t>
+          <t>7.90%11,700,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>7.90%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1040</v>
+        <v>989</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.96%5,350,000</t>
+          <t>7.86%5,350,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.96%</t>
+          <t>7.86%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.66%9880</t>
+          <t>-2.33%9650</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9880</v>
+        <v>9650</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.81%482,000</t>
+          <t>6.96%485,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>482000</v>
+        <v>485000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-7.34%959</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>959</v>
+        <v>3095</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.33%4,620,000</t>
+          <t>6.58%1,430,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.33%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4620000</v>
+        <v>1430000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-2.82%932</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3105</v>
+        <v>932</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.22%1,400,000</t>
+          <t>6.44%4,650,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>6.44%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1400000</v>
+        <v>4650000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,33 +936,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1250</v>
+        <v>1190</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.08%3,400,000</t>
+          <t>6.19%3,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.19%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3400000</v>
+        <v>3500000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4045</v>
+        <v>3915</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.07%1,050,000</t>
+          <t>6.11%1,050,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>6.11%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.19%312</t>
+          <t>-5.13%296</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.55%10,200,000</t>
+          <t>4.84%11,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.84%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10200000</v>
+        <v>11000000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.73%543</t>
+          <t>-7.55%502</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.19%5,400,000</t>
+          <t>4.03%5,400,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.13%767</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>767</v>
+        <v>6315</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.29%3,000,000</t>
+          <t>3.43%365,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3000000</v>
+        <v>365000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>-7.82%707</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6405</v>
+        <v>707</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.21%350,000</t>
+          <t>3.15%3,000,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>350000</v>
+        <v>3000000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.19%2575</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2575</v>
+        <v>668</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.95%800,000</t>
+          <t>2.98%3,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>800000</v>
+        <v>3000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:57</t>
+          <t>2026-10-30 23:07:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.82%16980</t>
+          <t>-7.96%2370</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16980</v>
+        <v>2370</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.68%110,500</t>
+          <t>2.82%800,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>110500</v>
+        <v>800000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>-5.95%15970</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>683</v>
+        <v>15970</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.34%2,400,000</t>
+          <t>2.62%110,500</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2400000</v>
+        <v>110500</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.27%98.6</t>
+          <t>-0.3%98.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>98.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.83%13,000,000</t>
+          <t>1.90%13,000,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>-5.85%1930</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5815</v>
+        <v>1930</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.41%170,000</t>
+          <t>0.49%170,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.49%2050</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2050</v>
+        <v>5430</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.50%170,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>170000</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.74%5190</t>
+          <t>-4.62%4950</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.74%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5190</v>
+        <v>4950</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>-4.75%4610</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4840</v>
+        <v>4610</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.64%318</t>
+          <t>0%318</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.76%261</t>
+          <t>+4.02%271.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>+4.02%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>261</v>
+        <v>271.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.39%248</t>
+          <t>-1.01%245.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>248</v>
+        <v>245.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.42%1945</t>
+          <t>-9.77%1755</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1945</v>
+        <v>1755</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1885</v>
+        <v>1810</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,21 +2090,21 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1755</v>
+        <v>1625</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-2.65%183.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1705</v>
+        <v>183.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.08%188.5</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>188.5</v>
+        <v>1615</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:58</t>
+          <t>2026-10-30 23:07:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-0.31%161.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1480</v>
+        <v>161.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.62%162</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>162</v>
+        <v>1335</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-6.57%156.5</t>
+          <t>-7.99%144</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>-7.99%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>156.5</v>
+        <v>144</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>-8.99%1265</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1390</v>
+        <v>1265</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.87%116.5</t>
+          <t>-0.43%116</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>116.5</v>
+        <v>116</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>-3.46%111.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>115.5</v>
+        <v>111.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.85%950</t>
+          <t>-4.63%906</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>950</v>
+        <v>906</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.38%794</t>
+          <t>+1.13%803</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.55%73.4</t>
+          <t>-1.09%72.6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>73.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.48%75.3</t>
+          <t>+0.66%75.8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>75.3</v>
+        <v>75.8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.47%536</t>
+          <t>-4.48%512</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.67%54.8</t>
+          <t>0%54.8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2880華南金</t>
+          <t>2884玉山金</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.62%50.1</t>
+          <t>+0.1%49.05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>50.1</v>
+        <v>49.05</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2884玉山金</t>
+          <t>2880華南金</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.34%49</t>
+          <t>+0.6%50.4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.34%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>49</v>
+        <v>50.4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%9,090</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2890永豐金</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.88%269.5</t>
+          <t>+0.11%46.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>269.5</v>
+        <v>46.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,450</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:00</t>
+          <t>2026-10-30 23:08:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2887台新新光金</t>
+          <t>2883凱基金</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.95%42.4</t>
+          <t>-1.82%37.8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>42.4</v>
+        <v>37.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:01</t>
+          <t>2026-10-30 23:08:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2890永豐金</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.32%46.45</t>
+          <t>-5.94%253.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>46.45</v>
+        <v>253.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,450</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:01</t>
+          <t>2026-10-30 23:08:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,30 +3310,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2883凱基金</t>
+          <t>2887台新新光金</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.13%38.5</t>
+          <t>-0.35%42.25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>38.5</v>
+        <v>42.25</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:01</t>
+          <t>2026-10-30 23:08:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.38%214</t>
+          <t>-3.27%207</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:01</t>
+          <t>2026-10-30 23:08:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.69%213.5</t>
+          <t>-5.39%202</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-5.39%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>213.5</v>
+        <v>202</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:01</t>
+          <t>2026-10-30 23:08:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.96%158</t>
+          <t>+1.27%160</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-30_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:58</t>
+          <t>2026-10-30 23:18:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:59</t>
+          <t>2026-10-30 23:18:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:01</t>
+          <t>2026-10-30 23:18:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:02</t>
+          <t>2026-10-30 23:18:58</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:02</t>
+          <t>2026-10-30 23:18:58</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:02</t>
+          <t>2026-10-30 23:18:58</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:02</t>
+          <t>2026-10-30 23:18:58</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:02</t>
+          <t>2026-10-30 23:18:58</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-30_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:54</t>
+          <t>2026-10-30 23:55:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:55</t>
+          <t>2026-10-30 23:55:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:56</t>
+          <t>2026-10-30 23:55:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:58</t>
+          <t>2026-10-30 23:55:58</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:58</t>
+          <t>2026-10-30 23:55:58</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:58</t>
+          <t>2026-10-30 23:55:58</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:58</t>
+          <t>2026-10-30 23:55:58</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:58</t>
+          <t>2026-10-30 23:55:58</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
